--- a/PalomeroGallagher_Zilles_2018/PalomeroGallagher_Zilles_2018_TableS3_registry_row.xlsx
+++ b/PalomeroGallagher_Zilles_2018/PalomeroGallagher_Zilles_2018_TableS3_registry_row.xlsx
@@ -1,38 +1,225 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30425"/>
   <workbookPr/>
-  <workbookProtection/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_97116D753B84BD34C8FD18113C64A3D39373BF46" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C916957-9FED-4BCA-9EC8-D950AFBE3E36}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HOW_TO_PASTE" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="HOW_TO_PASTE" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+  <si>
+    <t>Citation (APA 7th-Annotated)</t>
+  </si>
+  <si>
+    <t>sequence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOI if different from article or doi Alt </t>
+  </si>
+  <si>
+    <t>Item number</t>
+  </si>
+  <si>
+    <t>1st Author</t>
+  </si>
+  <si>
+    <t>other author(s)</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>Publication name</t>
+  </si>
+  <si>
+    <t>DOI (or Alt)</t>
+  </si>
+  <si>
+    <t>Item name</t>
+  </si>
+  <si>
+    <t>Item encoded</t>
+  </si>
+  <si>
+    <t>Public TSV match from AUTO_Public_TSV_FileList (generated by _tools/file_list.R; do not edit manually)</t>
+  </si>
+  <si>
+    <t>Item full original title</t>
+  </si>
+  <si>
+    <t>Source format</t>
+  </si>
+  <si>
+    <t>N.B.</t>
+  </si>
+  <si>
+    <t>Progress stage</t>
+  </si>
+  <si>
+    <t>Snapshot name if unchanged</t>
+  </si>
+  <si>
+    <t>Source URL link</t>
+  </si>
+  <si>
+    <t>Flags pre-addressed</t>
+  </si>
+  <si>
+    <t>Flags possible</t>
+  </si>
+  <si>
+    <t>Flags active (skips)</t>
+  </si>
+  <si>
+    <t>Topic</t>
+  </si>
+  <si>
+    <t>Taxon</t>
+  </si>
+  <si>
+    <t>Main Trait(s)</t>
+  </si>
+  <si>
+    <t>Other Trait(s)</t>
+  </si>
+  <si>
+    <t>Material type (e.g. histological, MRI)</t>
+  </si>
+  <si>
+    <t>Method</t>
+  </si>
+  <si>
+    <t>Measure type</t>
+  </si>
+  <si>
+    <t>Team</t>
+  </si>
+  <si>
+    <t>Collection</t>
+  </si>
+  <si>
+    <t>Data role (primary/secondary/both)</t>
+  </si>
+  <si>
+    <t>Source (if secondary)</t>
+  </si>
+  <si>
+    <t>recommendation</t>
+  </si>
+  <si>
+    <t>Palomero-Gallagher, N., &amp; Zilles, K. (2018). Differences in cytoarchitecture of Broca’s region between human, ape and macaque brains. Cortex. https://doi.org/10.1016/j.cortex.2018.09.008</t>
+  </si>
+  <si>
+    <t>TableS3</t>
+  </si>
+  <si>
+    <t>Supplementary table 3: Mean GLI (volume proportion of cell bodies per volume tissue) over all cortical layers, as well as in the supragranular, granular and infragranular strata of areas 44 and 45. Data pertaining figure 12.</t>
+  </si>
+  <si>
+    <t>digital-native xlsx (journal supplementary file mmc1.xlsx, sheet 'Table S3')</t>
+  </si>
+  <si>
+    <t>Per-specimen GLI summary; human 4 specimens, macaque 2-3, others single-specimen. Companion Tables S1/S2 (depth profiles, Figs. 10/11) not built in this item.</t>
+  </si>
+  <si>
+    <t>FINISHED</t>
+  </si>
+  <si>
+    <t>PalomeroGallagher_Zilles_2018_TableS3_snapshot.xlsx (byte-identical copy-rename of 1-s2.0-S0010945218302958-mmc1.xlsx)</t>
+  </si>
+  <si>
+    <t>cytoarchitecture; grey level index</t>
+  </si>
+  <si>
+    <t>Homo sapiens; Pan paniscus; Pan troglodytes; Gorilla gorilla; Pongo pygmaeus; Hylobates lar; Macaca fascicularis</t>
+  </si>
+  <si>
+    <t>grey level index (GLI, %), areas 44 and 45 (Broca-region homologs), by cortical stratum, per specimen</t>
+  </si>
+  <si>
+    <t>histological (cell-body stained sections)</t>
+  </si>
+  <si>
+    <t>layer-specific GLI image analysis</t>
+  </si>
+  <si>
+    <t>pct.GLI</t>
+  </si>
+  <si>
+    <t>primary</t>
+  </si>
+  <si>
+    <t>This paper already has a stub row in Sheet1 (Citation starts 'Palomero-Gallagher, N., &amp; Zilles, K. (2018)...', Item name 'PalomeroGallagher_Zilles_2018_' trailing underscore, Item number blank) - fill that row's Item number to 'TableS3' rather than appending a duplicate row.</t>
+  </si>
+  <si>
+    <t>Fill the EXISTING stub row for this paper (search Sheet1 for Citation starting</t>
+  </si>
+  <si>
+    <t>'Palomero-Gallagher, N., &amp; Zilles, K. (2018)...') by setting its Item number to 'TableS3'</t>
+  </si>
+  <si>
+    <t>(no spaces, so the Item-name formula resolves to 'PalomeroGallagher_Zilles_2018_TableS3',</t>
+  </si>
+  <si>
+    <t>matching the .R script's item_name) and pasting N-&gt;AG as VALUES from row 2 below.</t>
+  </si>
+  <si>
+    <t>Leave B, C, E-M blank/grey (formula-generated). After editing, run file_list.R, verify K</t>
+  </si>
+  <si>
+    <t>(Item encoded) has no trailing underscore, then re-run PalomeroGallagher_Zilles_2018_TableS3.R</t>
+  </si>
+  <si>
+    <t>to write the TSV into __Public/comparative-data/.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <color rgb="00808080"/>
+      <sz val="11"/>
+      <color rgb="FF808080"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -51,81 +238,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -413,274 +541,166 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AG2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Citation (APA 7th-Annotated)</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>sequence</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DOI if different from article or doi Alt </t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Item number</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>1st Author</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>other author(s)</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>year</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Publication name</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>DOI (or Alt)</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Item name</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Item encoded</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Public TSV match from AUTO_Public_TSV_FileList (generated by _tools/file_list.R; do not edit manually)</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Item full original title</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Source format</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>N.B.</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Progress stage</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Snapshot name if unchanged</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>Source URL link</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>Flags pre-addressed</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>Flags possible</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Flags active (skips)</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>Topic</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>Taxon</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>Main Trait(s)</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>Other Trait(s)</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>Material type (e.g. histological, MRI)</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>Method</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>Measure type</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>Team</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>Collection</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>Data role (primary/secondary/both)</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>Source (if secondary)</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>recommendation</t>
-        </is>
+    <row r="1" spans="1:33">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Palomero-Gallagher, N., &amp; Zilles, K. (2018). Differences in cytoarchitecture of Broca’s region between human, ape and macaque brains. Cortex. https://doi.org/10.1016/j.cortex.2018.09.008</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr"/>
-      <c r="C2" s="1" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>TableS3</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr"/>
-      <c r="F2" s="1" t="inlineStr"/>
-      <c r="G2" s="1" t="inlineStr"/>
-      <c r="H2" s="1" t="inlineStr"/>
-      <c r="I2" s="1" t="inlineStr"/>
-      <c r="J2" s="1" t="inlineStr"/>
-      <c r="K2" s="1" t="inlineStr"/>
-      <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Supplementary table 3: Mean GLI (volume proportion of cell bodies per volume tissue) over all cortical layers, as well as in the supragranular, granular and infragranular strata of areas 44 and 45. Data pertaining figure 12.</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>digital-native xlsx (journal supplementary file mmc1.xlsx, sheet 'Table S3')</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Per-specimen GLI summary; human 4 specimens, macaque 2-3, others single-specimen. Companion Tables S1/S2 (depth profiles, Figs. 10/11) not built in this item.</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>FINISHED</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>PalomeroGallagher_Zilles_2018_TableS3_snapshot.xlsx (byte-identical copy-rename of 1-s2.0-S0010945218302958-mmc1.xlsx)</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>cytoarchitecture; grey level index</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>Homo sapiens; Pan paniscus; Pan troglodytes; Gorilla gorilla; Pongo pygmaeus; Hylobates lar; Macaca fascicularis</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>grey level index (GLI, %), areas 44 and 45 (Broca-region homologs), by cortical stratum, per specimen</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>histological (cell-body stained sections)</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>layer-specific GLI image analysis</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>pct.GLI</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>primary</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>This paper already has a stub row in Sheet1 (Citation starts 'Palomero-Gallagher, N., &amp; Zilles, K. (2018)...', Item name 'PalomeroGallagher_Zilles_2018_' trailing underscore, Item number blank) - fill that row's Item number to 'TableS3' rather than appending a duplicate row.</t>
-        </is>
+    <row r="2" spans="1:33">
+      <c r="A2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>39</v>
+      </c>
+      <c r="V2" t="s">
+        <v>40</v>
+      </c>
+      <c r="W2" t="s">
+        <v>41</v>
+      </c>
+      <c r="X2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -689,61 +709,43 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Fill the EXISTING stub row for this paper (search Sheet1 for Citation starting</t>
-        </is>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>48</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>'Palomero-Gallagher, N., &amp; Zilles, K. (2018)...') by setting its Item number to 'TableS3'</t>
-        </is>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>49</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>(no spaces, so the Item-name formula resolves to 'PalomeroGallagher_Zilles_2018_TableS3',</t>
-        </is>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>50</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>matching the .R script's item_name) and pasting N-&gt;AG as VALUES from row 2 below.</t>
-        </is>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>51</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Leave B, C, E-M blank/grey (formula-generated). After editing, run file_list.R, verify K</t>
-        </is>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>52</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>(Item encoded) has no trailing underscore, then re-run PalomeroGallagher_Zilles_2018_TableS3.R</t>
-        </is>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>53</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>to write the TSV into __Public/comparative-data/.</t>
-        </is>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -752,6 +754,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
@@ -1006,28 +1028,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BEEA4E02-0AA1-4F99-8C0E-C0EFF74C7149}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D9A819D-68E8-4157-9EDA-CFB993B4DCD4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1035,5 +1037,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D9A819D-68E8-4157-9EDA-CFB993B4DCD4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BEEA4E02-0AA1-4F99-8C0E-C0EFF74C7149}"/>
 </file>